--- a/it_forms/018_penetration_testing_audit_form--it_forms.xlsx
+++ b/it_forms/018_penetration_testing_audit_form--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1145,8 +1145,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'windows'}</t>
+          <t>windows</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Windows'}</t>
+          <t>Windows</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'linux'}</t>
+          <t>linux</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Linux'}</t>
+          <t>Linux</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'macos'}</t>
+          <t>macos</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'macOS'}</t>
+          <t>macOS</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'critical'}</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Critical'}</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
